--- a/Анализ_законодательства_иностранных_государств_ЭДО.xlsx
+++ b/Анализ_законодательства_иностранных_государств_ЭДО.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,6 +108,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -588,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -598,6 +601,7 @@
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -636,6 +640,11 @@
           <t>Особенности для ЭДО</t>
         </is>
       </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Ссылка для проверки</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="78" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -673,6 +682,11 @@
           <t>База для национальных законов; не «ЭДО‑платформы», а правовой режим электронных сообщений и записей</t>
         </is>
       </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>https://uncitral.un.org/en/texts/ecommerce/modellaw/electronic_commerce</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="78" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -710,6 +724,11 @@
           <t>Самая детальная модель «пространства доверия»; ближе всего к уровням ПЭП/УНЭП/УКЭП в РФ</t>
         </is>
       </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:32014R0910</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="78" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -747,6 +766,11 @@
           <t>Доказательственный подход common law + ETDA 2023 (MLETR) + отдельная рамка цифровой идентичности</t>
         </is>
       </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>https://www.legislation.gov.uk/ukpga/2000/7/section/7</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="78" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -784,6 +808,11 @@
           <t>Либерально‑договорная модель: согласие сторон, сохраняемость записи, доказываемость</t>
         </is>
       </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>https://www.law.cornell.edu/uscode/text/15/chapter-96</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="78" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -821,6 +850,11 @@
           <t>Эталон «торгового» ЭДО: нейтральность + secure‑презумпции + электронные коносаменты</t>
         </is>
       </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>https://sso.agc.gov.sg/Act/ETA2010</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="78" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -858,6 +892,11 @@
           <t>PKI + явный список исключений + с 2026 отдельный режим электронных транспортных/торговых документов (MLETR‑логика)</t>
         </is>
       </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.wipo.int/wipolex/en/legislation/details/6563</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="78" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -895,6 +934,11 @@
           <t>Ближайший к РФ интеграционный контур трансграничного ЭДО</t>
         </is>
       </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>https://adilet.zan.kz/rus/docs/Z030000370_</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="78" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -932,8 +976,23 @@
           <t>Отдельно развит B2B‑ЭДО (счета‑фактуры) и кадровый ЭДО; слабее — MLETR и квалифицированный архив</t>
         </is>
       </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_112701/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -953,17 +1012,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Что добавить</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Что не переносить</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Горизонт</t>
         </is>
@@ -1112,198 +1171,216 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>UNCITRAL MLEC 1996</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>https://uncitral.un.org/en/texts/ecommerce/modellaw/electronic_commerce</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>UNCITRAL MLES 2001</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>https://uncitral.un.org/en/texts/ecommerce/modellaw/electronic_signatures</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>UNCITRAL MLETR 2017 + статус</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>https://uncitral.un.org/en/texts/ecommerce/modellaw/electronic_transferable_records/status</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>eIDAS 910/2014</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:32014R0910</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>eIDAS 2.0 2024/1183</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:32024R1183</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>UK ECA 2000 s.7</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>https://www.legislation.gov.uk/ukpga/2000/7/section/7</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>UK ETDA 2023</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>https://www.legislation.gov.uk/ukpga/2023/38</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>UK DVS trust framework 1.0</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>https://www.gov.uk/government/publications/uk-digital-verification-services-trust-framework-1-0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>US ESIGN, 15 U.S.C. ch. 96</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>https://www.law.cornell.edu/uscode/text/15/chapter-96</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Singapore ETA 2010</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>https://sso.agc.gov.sg/Act/ETA2010</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>China ESL (WIPO Lex)</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>https://www.wipo.int/wipolex/en/legislation/details/6563</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>China CAC electronic documents 2026</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>https://www.cac.gov.cn/2026-04/17/c_1778166821092785.htm</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Закон РК № 370</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>https://adilet.zan.kz/rus/docs/Z030000370_</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>ЕЭК Решение № 120</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>https://docs.eaeunion.org/documents/414/7596/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>ФЗ № 63‑ФЗ</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>https://www.consultant.ru/document/cons_doc_LAW_112701/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>ФЗ № 315‑ФЗ (04.08.2026)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>http://kremlin.ru/acts/news/80444</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>